--- a/exports/trend_1d/RBLBANK_full_report.xlsx
+++ b/exports/trend_1d/RBLBANK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>10.92</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42689</v>
+        <v>42690</v>
       </c>
       <c r="H2" t="n">
-        <v>363.65</v>
+        <v>354.05</v>
       </c>
       <c r="I2" t="n">
         <v>355.5723520561673</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K2" t="n">
-        <v>20.49</v>
+        <v>17.31</v>
       </c>
       <c r="L2" t="n">
         <v>6.71</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>19.37</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42744</v>
+        <v>42745</v>
       </c>
       <c r="H3" t="n">
-        <v>354.7</v>
+        <v>362.5</v>
       </c>
       <c r="I3" t="n">
         <v>356.8957684727363</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.18</v>
+        <v>-2.39</v>
       </c>
       <c r="L3" t="n">
         <v>5.89</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>7.46</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42880</v>
+        <v>42881</v>
       </c>
       <c r="H4" t="n">
-        <v>545.6</v>
+        <v>516.55</v>
       </c>
       <c r="I4" t="n">
         <v>523.8568943477453</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K4" t="n">
-        <v>50.51</v>
+        <v>42.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.79</v>
@@ -669,7 +716,7 @@
         <v>1.44</v>
       </c>
       <c r="N4" t="n">
-        <v>3.73</v>
+        <v>5.32</v>
       </c>
       <c r="O4" t="n">
         <v>2.2</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>15.22</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42928</v>
+        <v>42929</v>
       </c>
       <c r="H5" t="n">
-        <v>533.75</v>
+        <v>546.35</v>
       </c>
       <c r="I5" t="n">
         <v>543.0318689115834</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.33</v>
+        <v>-5.77</v>
       </c>
       <c r="L5" t="n">
         <v>8.02</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42955</v>
+        <v>42956</v>
       </c>
       <c r="H6" t="n">
-        <v>511.8</v>
+        <v>497.2</v>
       </c>
       <c r="I6" t="n">
         <v>499.4904183650089</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K6" t="n">
-        <v>-6.32</v>
+        <v>-9</v>
       </c>
       <c r="L6" t="n">
-        <v>7.35</v>
+        <v>9.73</v>
       </c>
       <c r="M6" t="n">
         <v>1.29</v>
       </c>
       <c r="N6" t="n">
-        <v>2.09</v>
+        <v>2.85</v>
       </c>
       <c r="O6" t="n">
         <v>2.36</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>9.539999999999999</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42976</v>
+        <v>42977</v>
       </c>
       <c r="H7" t="n">
-        <v>531.55</v>
+        <v>537.55</v>
       </c>
       <c r="I7" t="n">
         <v>534.1488916332396</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.91</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>8.91</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.87</v>
+        <v>1.12</v>
       </c>
       <c r="N7" t="n">
         <v>5.25</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>9.98</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43004</v>
+        <v>43005</v>
       </c>
       <c r="H8" t="n">
-        <v>510.25</v>
+        <v>500.9</v>
       </c>
       <c r="I8" t="n">
         <v>502.4984645194247</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.08</v>
+        <v>-6.82</v>
       </c>
       <c r="L8" t="n">
         <v>7.54</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.34</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43104</v>
+        <v>43105</v>
       </c>
       <c r="H9" t="n">
-        <v>517.4</v>
+        <v>539.7</v>
       </c>
       <c r="I9" t="n">
         <v>530.6183057759939</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.29</v>
+        <v>-7.75</v>
       </c>
       <c r="L9" t="n">
         <v>10.2</v>
@@ -954,7 +1061,7 @@
         <v>1.44</v>
       </c>
       <c r="N9" t="n">
-        <v>2.06</v>
+        <v>4.31</v>
       </c>
       <c r="O9" t="n">
         <v>-1.83</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>7.36</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43123</v>
+        <v>43124</v>
       </c>
       <c r="H10" t="n">
-        <v>536.7</v>
+        <v>514.2</v>
       </c>
       <c r="I10" t="n">
         <v>516.1199265863211</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-4.72</v>
       </c>
       <c r="L10" t="n">
-        <v>4.47</v>
+        <v>7.33</v>
       </c>
       <c r="M10" t="n">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="N10" t="n">
-        <v>1.74</v>
+        <v>4.19</v>
       </c>
       <c r="O10" t="n">
         <v>4.31</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,25 +1178,25 @@
         <v>9.16</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43194</v>
+        <v>43195</v>
       </c>
       <c r="H11" t="n">
-        <v>489.15</v>
+        <v>496.5</v>
       </c>
       <c r="I11" t="n">
         <v>492.3758369526515</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K11" t="n">
-        <v>4.87</v>
+        <v>3.44</v>
       </c>
       <c r="L11" t="n">
         <v>4.24</v>
       </c>
       <c r="M11" t="n">
-        <v>1.49</v>
+        <v>1.97</v>
       </c>
       <c r="N11" t="n">
         <v>3.86</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.09</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43238</v>
+        <v>43241</v>
       </c>
       <c r="H12" t="n">
-        <v>508.5</v>
+        <v>498.2</v>
       </c>
       <c r="I12" t="n">
         <v>500.126822454847</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K12" t="n">
-        <v>2.42</v>
+        <v>0.34</v>
       </c>
       <c r="L12" t="n">
         <v>0.91</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>7.15</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43258</v>
+        <v>43259</v>
       </c>
       <c r="H13" t="n">
-        <v>526.3</v>
+        <v>532.8</v>
       </c>
       <c r="I13" t="n">
         <v>529.8563592972019</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.64</v>
+        <v>-6.95</v>
       </c>
       <c r="L13" t="n">
-        <v>6.48</v>
+        <v>7.65</v>
       </c>
       <c r="M13" t="n">
         <v>0.8100000000000001</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.4</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43347</v>
+        <v>43348</v>
       </c>
       <c r="H14" t="n">
-        <v>608</v>
+        <v>593.55</v>
       </c>
       <c r="I14" t="n">
         <v>595.0791388102856</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K14" t="n">
-        <v>14.11</v>
+        <v>11.4</v>
       </c>
       <c r="L14" t="n">
         <v>2.12</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.83</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43410</v>
+        <v>43413</v>
       </c>
       <c r="H15" t="n">
-        <v>538.4</v>
+        <v>551.65</v>
       </c>
       <c r="I15" t="n">
         <v>548.670412429056</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K15" t="n">
-        <v>9.289999999999999</v>
+        <v>7.06</v>
       </c>
       <c r="L15" t="n">
         <v>3.95</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>12.47</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43629</v>
+        <v>43630</v>
       </c>
       <c r="H16" t="n">
-        <v>639.15</v>
+        <v>625.9</v>
       </c>
       <c r="I16" t="n">
         <v>639.1374642630825</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K16" t="n">
-        <v>15.86</v>
+        <v>13.46</v>
       </c>
       <c r="L16" t="n">
         <v>4.98</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>146</v>
+        <v>147</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>10.15</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43731</v>
+        <v>43732</v>
       </c>
       <c r="H17" t="n">
-        <v>398.35</v>
+        <v>401</v>
       </c>
       <c r="I17" t="n">
         <v>400.5446028396776</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K17" t="n">
-        <v>36.36</v>
+        <v>35.93</v>
       </c>
       <c r="L17" t="n">
         <v>5.93</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>21.35</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43738</v>
+        <v>43739</v>
       </c>
       <c r="H18" t="n">
-        <v>328.85</v>
+        <v>299.35</v>
       </c>
       <c r="I18" t="n">
         <v>315.376622944309</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>-17.99</v>
+        <v>-25.35</v>
       </c>
       <c r="L18" t="n">
-        <v>20.05</v>
+        <v>35.9</v>
       </c>
       <c r="M18" t="n">
         <v>1.21</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>33.24</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43777</v>
+        <v>43780</v>
       </c>
       <c r="H19" t="n">
-        <v>323.9</v>
+        <v>343.6</v>
       </c>
       <c r="I19" t="n">
         <v>339.3539910834678</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K19" t="n">
-        <v>-8.199999999999999</v>
+        <v>-14.78</v>
       </c>
       <c r="L19" t="n">
-        <v>13.11</v>
+        <v>15.73</v>
       </c>
       <c r="M19" t="n">
         <v>1.6</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>23.85</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43860</v>
+        <v>43861</v>
       </c>
       <c r="H20" t="n">
-        <v>322.35</v>
+        <v>318.3</v>
       </c>
       <c r="I20" t="n">
         <v>320.8420462057464</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.18</v>
+        <v>-7.36</v>
       </c>
       <c r="L20" t="n">
         <v>9.369999999999999</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>13.8</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43990</v>
+        <v>43991</v>
       </c>
       <c r="H21" t="n">
-        <v>132.5</v>
+        <v>140.55</v>
       </c>
       <c r="I21" t="n">
         <v>136.6307499673433</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K21" t="n">
-        <v>58.37</v>
+        <v>55.84</v>
       </c>
       <c r="L21" t="n">
         <v>9</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>22.07</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44081</v>
+        <v>44082</v>
       </c>
       <c r="H22" t="n">
-        <v>186.75</v>
+        <v>179.8</v>
       </c>
       <c r="I22" t="n">
         <v>180.9685318256114</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K22" t="n">
-        <v>32.87</v>
+        <v>27.93</v>
       </c>
       <c r="L22" t="n">
         <v>7.83</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>19.01</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44140</v>
+        <v>44141</v>
       </c>
       <c r="H23" t="n">
-        <v>185.8</v>
+        <v>193.25</v>
       </c>
       <c r="I23" t="n">
         <v>187.6473815266467</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.34</v>
+        <v>-7.48</v>
       </c>
       <c r="L23" t="n">
-        <v>5.03</v>
+        <v>9.98</v>
       </c>
       <c r="M23" t="n">
         <v>2.03</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>13.76</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H24" t="n">
-        <v>227.65</v>
+        <v>206.55</v>
       </c>
       <c r="I24" t="n">
         <v>214.045984892771</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K24" t="n">
-        <v>17.8</v>
+        <v>6.88</v>
       </c>
       <c r="L24" t="n">
         <v>4.71</v>
@@ -1809,7 +2096,7 @@
         <v>1.92</v>
       </c>
       <c r="N24" t="n">
-        <v>4.18</v>
+        <v>9.27</v>
       </c>
       <c r="O24" t="n">
         <v>4.01</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>19.75</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44197</v>
+        <v>44200</v>
       </c>
       <c r="H25" t="n">
-        <v>231.05</v>
+        <v>239.6</v>
       </c>
       <c r="I25" t="n">
         <v>237.4643718118529</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>-11.86</v>
+        <v>-16</v>
       </c>
       <c r="L25" t="n">
-        <v>14.94</v>
+        <v>16.63</v>
       </c>
       <c r="M25" t="n">
         <v>1.2</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>12.69</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44217</v>
+        <v>44218</v>
       </c>
       <c r="H26" t="n">
-        <v>250.55</v>
+        <v>232.8</v>
       </c>
       <c r="I26" t="n">
         <v>237.3637511514584</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K26" t="n">
-        <v>4.57</v>
+        <v>-2.84</v>
       </c>
       <c r="L26" t="n">
-        <v>3.34</v>
+        <v>4.53</v>
       </c>
       <c r="M26" t="n">
         <v>1.15</v>
       </c>
       <c r="N26" t="n">
-        <v>3.74</v>
+        <v>7.08</v>
       </c>
       <c r="O26" t="n">
         <v>3.7</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>18.48</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44229</v>
+        <v>44230</v>
       </c>
       <c r="H27" t="n">
-        <v>242.4</v>
+        <v>256.55</v>
       </c>
       <c r="I27" t="n">
         <v>252.5332164453044</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.12</v>
+        <v>-10.2</v>
       </c>
       <c r="L27" t="n">
-        <v>7.67</v>
+        <v>12.71</v>
       </c>
       <c r="M27" t="n">
         <v>2.28</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>20.65</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44278</v>
+        <v>44279</v>
       </c>
       <c r="H28" t="n">
-        <v>226.8</v>
+        <v>215.9</v>
       </c>
       <c r="I28" t="n">
         <v>218.3922904536774</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K28" t="n">
-        <v>-11.6</v>
+        <v>-15.84</v>
       </c>
       <c r="L28" t="n">
         <v>16.43</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>17.08</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44335</v>
+        <v>44336</v>
       </c>
       <c r="H29" t="n">
-        <v>199.95</v>
+        <v>204.25</v>
       </c>
       <c r="I29" t="n">
         <v>203.9200842688275</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K29" t="n">
-        <v>7.39</v>
+        <v>5.4</v>
       </c>
       <c r="L29" t="n">
         <v>4.42</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>10.36</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44400</v>
+        <v>44403</v>
       </c>
       <c r="H30" t="n">
-        <v>204.5</v>
+        <v>198.45</v>
       </c>
       <c r="I30" t="n">
         <v>202.0280732851234</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K30" t="n">
-        <v>0.12</v>
+        <v>-2.84</v>
       </c>
       <c r="L30" t="n">
-        <v>1.91</v>
+        <v>3.01</v>
       </c>
       <c r="M30" t="n">
         <v>2.3</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>10.41</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44453</v>
+        <v>44454</v>
       </c>
       <c r="H31" t="n">
-        <v>175.35</v>
+        <v>179.4</v>
       </c>
       <c r="I31" t="n">
         <v>177.665633995464</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K31" t="n">
-        <v>11.64</v>
+        <v>9.6</v>
       </c>
       <c r="L31" t="n">
         <v>3.65</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>8.06</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44497</v>
+        <v>44498</v>
       </c>
       <c r="H32" t="n">
-        <v>201.05</v>
+        <v>180.55</v>
       </c>
       <c r="I32" t="n">
         <v>187.2512009472208</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K32" t="n">
-        <v>12.07</v>
+        <v>0.64</v>
       </c>
       <c r="L32" t="n">
         <v>5.16</v>
       </c>
       <c r="M32" t="n">
-        <v>1.49</v>
+        <v>8.33</v>
       </c>
       <c r="N32" t="n">
-        <v>4.42</v>
+        <v>10.2</v>
       </c>
       <c r="O32" t="n">
         <v>2.31</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>15.55</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44508</v>
+        <v>44509</v>
       </c>
       <c r="H33" t="n">
-        <v>204.15</v>
+        <v>217.25</v>
       </c>
       <c r="I33" t="n">
         <v>208.625199509476</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K33" t="n">
-        <v>-13.07</v>
+        <v>-20.33</v>
       </c>
       <c r="L33" t="n">
-        <v>16.73</v>
+        <v>21.52</v>
       </c>
       <c r="M33" t="n">
         <v>1.62</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>16.67</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H34" t="n">
-        <v>200.5</v>
+        <v>185.85</v>
       </c>
       <c r="I34" t="n">
         <v>188.3835563227361</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K34" t="n">
-        <v>-7.71</v>
+        <v>-14.45</v>
       </c>
       <c r="L34" t="n">
-        <v>12.38</v>
+        <v>14.84</v>
       </c>
       <c r="M34" t="n">
-        <v>0.88</v>
+        <v>1.32</v>
       </c>
       <c r="N34" t="n">
-        <v>4.92</v>
+        <v>7.31</v>
       </c>
       <c r="O34" t="n">
         <v>6.42</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>18.17</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44762</v>
+        <v>44763</v>
       </c>
       <c r="H35" t="n">
-        <v>91.45</v>
+        <v>94.95</v>
       </c>
       <c r="I35" t="n">
         <v>94.28306933285089</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K35" t="n">
-        <v>50.79</v>
+        <v>48.91</v>
       </c>
       <c r="L35" t="n">
         <v>10.52</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>163</v>
+        <v>164</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>8</v>
+      </c>
+      <c r="U35" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>15.36</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H36" t="n">
-        <v>123</v>
+        <v>112.55</v>
       </c>
       <c r="I36" t="n">
         <v>115.3905645555956</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K36" t="n">
-        <v>29.54</v>
+        <v>18.54</v>
       </c>
       <c r="L36" t="n">
         <v>5.85</v>
@@ -2493,7 +2924,7 @@
         <v>5.91</v>
       </c>
       <c r="N36" t="n">
-        <v>4.82</v>
+        <v>8.5</v>
       </c>
       <c r="O36" t="n">
         <v>3.83</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>19.36</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44851</v>
+        <v>44852</v>
       </c>
       <c r="H37" t="n">
-        <v>127.05</v>
+        <v>129.35</v>
       </c>
       <c r="I37" t="n">
         <v>127.6600725889351</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K37" t="n">
-        <v>-12.88</v>
+        <v>-14.93</v>
       </c>
       <c r="L37" t="n">
-        <v>13.33</v>
+        <v>16.39</v>
       </c>
       <c r="M37" t="n">
         <v>3.38</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>11.5</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H38" t="n">
-        <v>162.1</v>
+        <v>151.3</v>
       </c>
       <c r="I38" t="n">
         <v>153.5584834084167</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K38" t="n">
-        <v>25.32</v>
+        <v>16.97</v>
       </c>
       <c r="L38" t="n">
         <v>7.61</v>
@@ -2607,7 +3062,7 @@
         <v>1.68</v>
       </c>
       <c r="N38" t="n">
-        <v>4.47</v>
+        <v>6.66</v>
       </c>
       <c r="O38" t="n">
         <v>1.81</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>16.52</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44923</v>
+        <v>44924</v>
       </c>
       <c r="H39" t="n">
-        <v>173.05</v>
+        <v>176.5</v>
       </c>
       <c r="I39" t="n">
         <v>176.3011107189476</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K39" t="n">
-        <v>-14.38</v>
+        <v>-16.66</v>
       </c>
       <c r="L39" t="n">
-        <v>15.17</v>
+        <v>17.12</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>15.3</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44949</v>
+        <v>44950</v>
       </c>
       <c r="H40" t="n">
-        <v>167.4</v>
+        <v>160.75</v>
       </c>
       <c r="I40" t="n">
         <v>164.537423575657</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K40" t="n">
-        <v>-5.16</v>
+        <v>-8.92</v>
       </c>
       <c r="L40" t="n">
-        <v>6.23</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M40" t="n">
         <v>0.64</v>
       </c>
       <c r="N40" t="n">
-        <v>3.59</v>
+        <v>3.97</v>
       </c>
       <c r="O40" t="n">
         <v>1.99</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>13.83</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45029</v>
+        <v>45033</v>
       </c>
       <c r="H41" t="n">
-        <v>147.1</v>
+        <v>154.35</v>
       </c>
       <c r="I41" t="n">
         <v>151.8912677997088</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K41" t="n">
-        <v>8.49</v>
+        <v>3.98</v>
       </c>
       <c r="L41" t="n">
         <v>6.07</v>
@@ -2778,7 +3269,7 @@
         <v>1.51</v>
       </c>
       <c r="N41" t="n">
-        <v>4.75</v>
+        <v>4.93</v>
       </c>
       <c r="O41" t="n">
         <v>-3.97</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>12.72</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45062</v>
+        <v>45063</v>
       </c>
       <c r="H42" t="n">
-        <v>149.45</v>
+        <v>144.65</v>
       </c>
       <c r="I42" t="n">
         <v>146.3277284119634</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.17</v>
+        <v>-6.28</v>
       </c>
       <c r="L42" t="n">
-        <v>5.57</v>
+        <v>7</v>
       </c>
       <c r="M42" t="n">
         <v>1.55</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>11.91</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45075</v>
+        <v>45076</v>
       </c>
       <c r="H43" t="n">
-        <v>153.75</v>
+        <v>163</v>
       </c>
       <c r="I43" t="n">
         <v>157.3463449744917</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K43" t="n">
-        <v>-6.29</v>
+        <v>-12.69</v>
       </c>
       <c r="L43" t="n">
-        <v>6.81</v>
+        <v>13.17</v>
       </c>
       <c r="M43" t="n">
         <v>0.9</v>
       </c>
       <c r="N43" t="n">
-        <v>3.64</v>
+        <v>6.02</v>
       </c>
       <c r="O43" t="n">
         <v>-3.21</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>12.55</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45224</v>
+        <v>45225</v>
       </c>
       <c r="H44" t="n">
-        <v>225.45</v>
+        <v>216.35</v>
       </c>
       <c r="I44" t="n">
         <v>225.1364904875373</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K44" t="n">
-        <v>38.31</v>
+        <v>32.73</v>
       </c>
       <c r="L44" t="n">
         <v>6.17</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>15.17</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45243</v>
+        <v>45245</v>
       </c>
       <c r="H45" t="n">
-        <v>245.8</v>
+        <v>252.6</v>
       </c>
       <c r="I45" t="n">
         <v>249.1706272768322</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K45" t="n">
-        <v>-13.61</v>
+        <v>-16.76</v>
       </c>
       <c r="L45" t="n">
-        <v>14.58</v>
+        <v>17.86</v>
       </c>
       <c r="M45" t="n">
         <v>1.31</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>9.76</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45247</v>
+        <v>45250</v>
       </c>
       <c r="H46" t="n">
-        <v>234.8</v>
+        <v>229.1</v>
       </c>
       <c r="I46" t="n">
         <v>231.3909857817421</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K46" t="n">
-        <v>-7.05</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>8.869999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="M46" t="n">
         <v>5.95</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>13.86</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="H47" t="n">
-        <v>256.15</v>
+        <v>267.7</v>
       </c>
       <c r="I47" t="n">
         <v>258.4331777090184</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K47" t="n">
-        <v>-11.81</v>
+        <v>-16.85</v>
       </c>
       <c r="L47" t="n">
-        <v>14.8</v>
+        <v>20.69</v>
       </c>
       <c r="M47" t="n">
         <v>1.65</v>
       </c>
       <c r="N47" t="n">
-        <v>4.01</v>
+        <v>4.51</v>
       </c>
       <c r="O47" t="n">
         <v>-2.43</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>11.28</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45311</v>
+        <v>45314</v>
       </c>
       <c r="H48" t="n">
-        <v>268.7</v>
+        <v>253.35</v>
       </c>
       <c r="I48" t="n">
         <v>261.2337846341632</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K48" t="n">
-        <v>0.37</v>
+        <v>-5.36</v>
       </c>
       <c r="L48" t="n">
-        <v>3.96</v>
+        <v>6.99</v>
       </c>
       <c r="M48" t="n">
         <v>3.13</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>19.64</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45390</v>
+        <v>45391</v>
       </c>
       <c r="H49" t="n">
-        <v>255.5</v>
+        <v>258.8</v>
       </c>
       <c r="I49" t="n">
         <v>258.0384728947645</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.85</v>
+        <v>-2.15</v>
       </c>
       <c r="L49" t="n">
         <v>10.18</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H50" t="n">
-        <v>247.5</v>
+        <v>239.9</v>
       </c>
       <c r="I50" t="n">
         <v>242.4273738840323</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K50" t="n">
-        <v>-4.37</v>
+        <v>-7.3</v>
       </c>
       <c r="L50" t="n">
         <v>8.289999999999999</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>13.45</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45524</v>
+        <v>45525</v>
       </c>
       <c r="H51" t="n">
-        <v>218.72</v>
+        <v>228.1</v>
       </c>
       <c r="I51" t="n">
         <v>227.4948049618493</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K51" t="n">
-        <v>8.83</v>
+        <v>4.92</v>
       </c>
       <c r="L51" t="n">
         <v>12.71</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>11.44</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45541</v>
+        <v>45544</v>
       </c>
       <c r="H52" t="n">
-        <v>212.22</v>
+        <v>210.03</v>
       </c>
       <c r="I52" t="n">
         <v>210.2907694645307</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K52" t="n">
-        <v>-6.96</v>
+        <v>-7.92</v>
       </c>
       <c r="L52" t="n">
-        <v>7.47</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M52" t="n">
         <v>2.63</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45629</v>
+        <v>45630</v>
       </c>
       <c r="H53" t="n">
-        <v>162.71</v>
+        <v>173.4</v>
       </c>
       <c r="I53" t="n">
         <v>170.3029287734108</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K53" t="n">
-        <v>22.53</v>
+        <v>17.44</v>
       </c>
       <c r="L53" t="n">
         <v>3.99</v>
@@ -3462,7 +4097,7 @@
         <v>1.49</v>
       </c>
       <c r="N53" t="n">
-        <v>4.33</v>
+        <v>6.57</v>
       </c>
       <c r="O53" t="n">
         <v>-1.03</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>14.23</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H54" t="n">
-        <v>164.33</v>
+        <v>152.79</v>
       </c>
       <c r="I54" t="n">
         <v>158.6249031247568</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K54" t="n">
-        <v>-5.23</v>
+        <v>-11.89</v>
       </c>
       <c r="L54" t="n">
-        <v>6.34</v>
+        <v>12.77</v>
       </c>
       <c r="M54" t="n">
         <v>1.74</v>
       </c>
       <c r="N54" t="n">
-        <v>3.18</v>
+        <v>7.02</v>
       </c>
       <c r="O54" t="n">
         <v>6.57</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>17.35</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45692</v>
+        <v>45693</v>
       </c>
       <c r="H55" t="n">
-        <v>166.16</v>
+        <v>170.85</v>
       </c>
       <c r="I55" t="n">
         <v>169.3160848378314</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K55" t="n">
-        <v>-8.75</v>
+        <v>-11.82</v>
       </c>
       <c r="L55" t="n">
-        <v>11.05</v>
+        <v>14.21</v>
       </c>
       <c r="M55" t="n">
         <v>1.78</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>11.02</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45705</v>
+        <v>45706</v>
       </c>
       <c r="H56" t="n">
-        <v>155.8</v>
+        <v>150.97</v>
       </c>
       <c r="I56" t="n">
         <v>152.0290535079311</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K56" t="n">
-        <v>-8.81</v>
+        <v>-11.64</v>
       </c>
       <c r="L56" t="n">
-        <v>10.91</v>
+        <v>12.26</v>
       </c>
       <c r="M56" t="n">
         <v>0.97</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>15.26</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H57" t="n">
-        <v>168.3</v>
+        <v>175.12</v>
       </c>
       <c r="I57" t="n">
         <v>174.0112064954902</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K57" t="n">
-        <v>-11.48</v>
+        <v>-16</v>
       </c>
       <c r="L57" t="n">
-        <v>12.6</v>
+        <v>17.24</v>
       </c>
       <c r="M57" t="n">
         <v>3.45</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>12.26</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="H58" t="n">
-        <v>304.3</v>
+        <v>298.45</v>
       </c>
       <c r="I58" t="n">
         <v>301.6437177514561</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K58" t="n">
-        <v>73.77</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="L58" t="n">
         <v>6.12</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>173</v>
+        <v>174</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>10</v>
+      </c>
+      <c r="U58" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>8.25</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="H59" t="n">
-        <v>312</v>
+        <v>324.6</v>
       </c>
       <c r="I59" t="n">
         <v>322.3266827046674</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K59" t="n">
-        <v>-4.54</v>
+        <v>-8.76</v>
       </c>
       <c r="L59" t="n">
-        <v>8.66</v>
+        <v>10.05</v>
       </c>
       <c r="M59" t="n">
         <v>1.22</v>
       </c>
       <c r="N59" t="n">
-        <v>3.05</v>
+        <v>4.04</v>
       </c>
       <c r="O59" t="n">
         <v>-1.92</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>9.32</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H60" t="n">
-        <v>302.85</v>
+        <v>293.7</v>
       </c>
       <c r="I60" t="n">
         <v>294.3410019222545</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K60" t="n">
-        <v>-6.7</v>
+        <v>-9.52</v>
       </c>
       <c r="L60" t="n">
-        <v>8.460000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="M60" t="n">
         <v>4.81</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>13.07</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="H61" t="n">
-        <v>322.25</v>
+        <v>325.8</v>
       </c>
       <c r="I61" t="n">
         <v>322.9050040316133</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K61" t="n">
-        <v>-9.720000000000001</v>
+        <v>-10.93</v>
       </c>
       <c r="L61" t="n">
-        <v>10.78</v>
+        <v>11.46</v>
       </c>
       <c r="M61" t="n">
         <v>2.44</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>8.1</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H62" t="n">
-        <v>313.15</v>
+        <v>306.05</v>
       </c>
       <c r="I62" t="n">
         <v>306.628280193033</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.88</v>
+        <v>-6.06</v>
       </c>
       <c r="L62" t="n">
-        <v>5.56</v>
+        <v>6.77</v>
       </c>
       <c r="M62" t="n">
         <v>3.05</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,25 +4766,25 @@
         <v>9.85</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H63" t="n">
-        <v>312.6</v>
+        <v>322.85</v>
       </c>
       <c r="I63" t="n">
         <v>318.8072839557568</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.14</v>
+        <v>-5.49</v>
       </c>
       <c r="L63" t="n">
-        <v>4.51</v>
+        <v>6.78</v>
       </c>
       <c r="M63" t="n">
-        <v>2.64</v>
+        <v>3.65</v>
       </c>
       <c r="N63" t="n">
         <v>5.7</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>10.4</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="H64" t="n">
-        <v>417.7</v>
+        <v>388.05</v>
       </c>
       <c r="I64" t="n">
         <v>392.8871416677216</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K64" t="n">
-        <v>29.38</v>
+        <v>20.2</v>
       </c>
       <c r="L64" t="n">
         <v>5.19</v>
       </c>
       <c r="M64" t="n">
-        <v>2.69</v>
+        <v>4.24</v>
       </c>
       <c r="N64" t="n">
-        <v>4.08</v>
+        <v>7.1</v>
       </c>
       <c r="O64" t="n">
         <v>3.28</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>7</v>
+      </c>
+      <c r="U64" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -4149,6 +4928,14 @@
       <c r="Q65" t="n">
         <v>11</v>
       </c>
+      <c r="R65" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8461,7 +9248,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="6">
@@ -8471,7 +9258,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -8481,7 +9268,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8">
@@ -8491,7 +9278,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -8501,7 +9288,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
@@ -8511,7 +9298,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>123.8</v>
+        <v>124.8</v>
       </c>
     </row>
     <row r="11">
@@ -8551,7 +9338,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.13</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="15">
@@ -8561,7 +9348,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.15</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="16">
@@ -8571,7 +9358,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.01</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="17">
@@ -8581,7 +9368,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>73.77</v>
+        <v>70.43000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -8591,7 +9378,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>41.3</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="19">
@@ -8601,7 +9388,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.99</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="20">
@@ -8611,7 +9398,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.35</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -8621,7 +9408,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20.05</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="22">
@@ -8631,7 +9418,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
@@ -8641,7 +9428,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
@@ -8651,7 +9438,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.49</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="25">
@@ -8671,7 +9458,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.38</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="27">
@@ -8691,7 +9478,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29">
